--- a/Configs/GameConfig/Datas/event.xlsx
+++ b/Configs/GameConfig/Datas/event.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -82,10 +82,7 @@
     <t>type</t>
   </si>
   <si>
-    <t>effect_id</t>
-  </si>
-  <si>
-    <t>pre_courseIds</t>
+    <t>action_param_int</t>
   </si>
   <si>
     <t>need_itemIds</t>
@@ -124,10 +121,7 @@
     <t>GameEventType</t>
   </si>
   <si>
-    <t>int#ref=TbEffect</t>
-  </si>
-  <si>
-    <t>(list#sep=;),int#ref=TbEvent</t>
+    <t>array,int</t>
   </si>
   <si>
     <t>(list#sep=;),int#ref=TbItem</t>
@@ -142,26 +136,7 @@
     <t>##</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>这是i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>d</t>
-    </r>
+    <t>id</t>
   </si>
   <si>
     <t>名字</t>
@@ -170,10 +145,7 @@
     <t>描述</t>
   </si>
   <si>
-    <t>效果id</t>
-  </si>
-  <si>
-    <t>前置事件</t>
+    <t>操作参数</t>
   </si>
   <si>
     <t>需要道具</t>
@@ -191,10 +163,10 @@
     <t>完成增加属性</t>
   </si>
   <si>
-    <t>文字课</t>
-  </si>
-  <si>
-    <t>Course</t>
+    <t>测试对话</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
   </si>
 </sst>
 </file>
@@ -823,12 +795,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1148,73 +1138,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:AH23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="2" max="2" width="14.875" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="12.3833333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.625" customWidth="1"/>
-    <col min="6" max="6" width="20.75" customWidth="1"/>
-    <col min="7" max="7" width="39.75" customWidth="1"/>
-    <col min="8" max="8" width="27.625" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="21.875" customWidth="1"/>
-    <col min="11" max="11" width="23.125" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="19.375" customWidth="1"/>
-    <col min="15" max="15" width="21.75" customWidth="1"/>
+    <col min="5" max="5" width="16.25" customWidth="1"/>
+    <col min="6" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="22.875" customWidth="1"/>
+    <col min="10" max="10" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="21.875" customWidth="1"/>
+    <col min="12" max="12" width="23.125" customWidth="1"/>
+    <col min="13" max="13" width="19.875" customWidth="1"/>
+    <col min="14" max="14" width="21.25" customWidth="1"/>
+    <col min="15" max="15" width="19.375" customWidth="1"/>
+    <col min="16" max="16" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:33">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:34">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1"/>
       <c r="Q1"/>
       <c r="R1"/>
       <c r="S1"/>
@@ -1232,26 +1219,27 @@
       <c r="AE1"/>
       <c r="AF1"/>
       <c r="AG1"/>
+      <c r="AH1"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:33">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:34">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
       <c r="Q2"/>
       <c r="R2"/>
       <c r="S2"/>
@@ -1269,54 +1257,53 @@
       <c r="AE2"/>
       <c r="AF2"/>
       <c r="AG2"/>
+      <c r="AH2"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:33">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:34">
+      <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P3"/>
+      <c r="J3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q3"/>
       <c r="R3"/>
       <c r="S3"/>
@@ -1334,28 +1321,29 @@
       <c r="AE3"/>
       <c r="AF3"/>
       <c r="AG3"/>
+      <c r="AH3"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:33">
-      <c r="A4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4"/>
+    <row r="4" s="2" customFormat="1" spans="1:34">
+      <c r="A4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
       <c r="Q4"/>
       <c r="R4"/>
       <c r="S4"/>
@@ -1373,46 +1361,49 @@
       <c r="AE4"/>
       <c r="AF4"/>
       <c r="AG4"/>
+      <c r="AH4"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:33">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:34">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="L5" s="4"/>
+      <c r="M5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="N5" s="4"/>
+      <c r="O5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="3"/>
-      <c r="P5"/>
+      <c r="P5" s="4"/>
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5"/>
@@ -1430,25 +1421,38 @@
       <c r="AE5"/>
       <c r="AF5"/>
       <c r="AG5"/>
+      <c r="AH5"/>
     </row>
-    <row r="6" spans="2:9">
-      <c r="B6">
+    <row r="6" spans="2:10">
+      <c r="B6" s="3">
         <v>10001</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6">
-        <v>1000100001</v>
-      </c>
-      <c r="I6">
+        <v>33</v>
+      </c>
+      <c r="J6">
         <v>30</v>
       </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="3">
+        <v>1000101</v>
+      </c>
+    </row>
+    <row r="23" spans="7:8">
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F4:H4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
